--- a/pending.xlsx
+++ b/pending.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/chandanmallik/projects/skfinance/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A3FF024-8789-2A49-8C60-AE8E4F6FB523}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2D28573-D5BD-404F-9096-9738D79077B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3980" yWindow="2780" windowWidth="28040" windowHeight="17180" xr2:uid="{1DC1BFDF-9E2F-1742-9CDD-20C92B7A1FA7}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="21">
   <si>
     <t>dealer</t>
   </si>
@@ -99,6 +99,9 @@
   </si>
   <si>
     <t>whatsapp templet system</t>
+  </si>
+  <si>
+    <t>Dealer onboarding pattern auto generate</t>
   </si>
 </sst>
 </file>
@@ -508,11 +511,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0A959E5B-E098-6D4B-A7D3-C4C8EE0E90BF}">
-  <dimension ref="A1:D13"/>
+  <dimension ref="A1:D14"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
-    <col min="1" max="1" width="9" customWidth="1"/>
-    <col min="3" max="3" width="77.6640625" customWidth="1"/>
+    <col min="1" max="1" width="4.1640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="6.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="74.6640625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="16.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -568,6 +572,9 @@
       <c r="C4" t="s">
         <v>3</v>
       </c>
+      <c r="D4" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="1">
@@ -637,6 +644,9 @@
       <c r="C10" t="s">
         <v>13</v>
       </c>
+      <c r="D10" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="11" spans="1:4">
       <c r="A11" s="1">
@@ -648,6 +658,9 @@
       <c r="C11" s="3" t="s">
         <v>16</v>
       </c>
+      <c r="D11" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="12" spans="1:4">
       <c r="A12" s="1">
@@ -659,6 +672,9 @@
       <c r="C12" s="3" t="s">
         <v>17</v>
       </c>
+      <c r="D12" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="13" spans="1:4">
       <c r="A13" s="1">
@@ -669,6 +685,17 @@
       </c>
       <c r="C13" s="3" t="s">
         <v>18</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4">
+      <c r="A14" s="1">
+        <v>14</v>
+      </c>
+      <c r="B14" t="s">
+        <v>0</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>20</v>
       </c>
     </row>
   </sheetData>

--- a/pending.xlsx
+++ b/pending.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/chandanmallik/projects/skfinance/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2D28573-D5BD-404F-9096-9738D79077B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E936493-9673-2745-B1FF-7DEA53C74C59}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3980" yWindow="2780" windowWidth="28040" windowHeight="17180" xr2:uid="{1DC1BFDF-9E2F-1742-9CDD-20C92B7A1FA7}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="21">
   <si>
     <t>dealer</t>
   </si>
@@ -586,6 +586,9 @@
       <c r="C5" t="s">
         <v>8</v>
       </c>
+      <c r="D5" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="1">
@@ -597,6 +600,9 @@
       <c r="C6" t="s">
         <v>9</v>
       </c>
+      <c r="D6" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="1">
@@ -633,6 +639,9 @@
       <c r="C9" t="s">
         <v>11</v>
       </c>
+      <c r="D9" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="1">
@@ -686,6 +695,9 @@
       <c r="C13" s="3" t="s">
         <v>18</v>
       </c>
+      <c r="D13" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="14" spans="1:4">
       <c r="A14" s="1">
@@ -696,6 +708,9 @@
       </c>
       <c r="C14" s="3" t="s">
         <v>20</v>
+      </c>
+      <c r="D14" t="s">
+        <v>14</v>
       </c>
     </row>
   </sheetData>
